--- a/INCREMENTO 2/Burn-up.xlsx
+++ b/INCREMENTO 2/Burn-up.xlsx
@@ -34,7 +34,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -44,11 +44,6 @@
     <font>
       <color theme="1"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">
@@ -111,16 +106,14 @@
     <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
     <xf borderId="0" fillId="5" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="6" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="7" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="7" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="6" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -396,18 +389,18 @@
         <v>0.0</v>
       </c>
       <c r="C2" s="6">
-        <v>4.84</v>
+        <v>5.06060606061</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="4">
         <v>45902.0</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="5">
         <v>7.0</v>
       </c>
       <c r="C3" s="6">
-        <v>9.68</v>
+        <v>10.1212121212</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
@@ -415,10 +408,10 @@
         <v>45903.0</v>
       </c>
       <c r="B4" s="7">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="C4" s="6">
-        <v>14.52</v>
+        <v>15.1818181822</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
@@ -426,10 +419,10 @@
         <v>45904.0</v>
       </c>
       <c r="B5" s="7">
-        <v>14.0</v>
+        <v>13.0</v>
       </c>
       <c r="C5" s="6">
-        <v>19.36</v>
+        <v>20.2424242429267</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
@@ -437,10 +430,10 @@
         <v>45905.0</v>
       </c>
       <c r="B6" s="7">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="C6" s="6">
-        <v>24.2</v>
+        <v>25.3030303037217</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
@@ -448,10 +441,10 @@
         <v>45906.0</v>
       </c>
       <c r="B7" s="7">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
       <c r="C7" s="6">
-        <v>29.04</v>
+        <v>30.3636363645167</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
@@ -459,10 +452,10 @@
         <v>45907.0</v>
       </c>
       <c r="B8" s="7">
-        <v>42.0</v>
+        <v>43.0</v>
       </c>
       <c r="C8" s="6">
-        <v>33.88</v>
+        <v>35.4242424253117</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
@@ -470,21 +463,21 @@
         <v>45908.0</v>
       </c>
       <c r="B9" s="7">
-        <v>54.0</v>
+        <v>55.0</v>
       </c>
       <c r="C9" s="6">
-        <v>38.72</v>
+        <v>40.4848484861067</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="4">
         <v>45909.0</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="5">
         <v>66.0</v>
       </c>
       <c r="C10" s="6">
-        <v>43.56</v>
+        <v>45.5454545469017</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
@@ -492,10 +485,10 @@
         <v>45910.0</v>
       </c>
       <c r="B11" s="7">
-        <v>76.0</v>
+        <v>78.0</v>
       </c>
       <c r="C11" s="6">
-        <v>48.4</v>
+        <v>50.6060606076967</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
@@ -503,10 +496,10 @@
         <v>45911.0</v>
       </c>
       <c r="B12" s="7">
-        <v>86.0</v>
+        <v>87.0</v>
       </c>
       <c r="C12" s="6">
-        <v>53.24</v>
+        <v>55.6666666684917</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
@@ -514,21 +507,21 @@
         <v>45912.0</v>
       </c>
       <c r="B13" s="7">
-        <v>94.0</v>
+        <v>98.0</v>
       </c>
       <c r="C13" s="6">
-        <v>58.08</v>
+        <v>60.7272727292867</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="4">
         <v>45913.0</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="5">
         <v>107.0</v>
       </c>
       <c r="C14" s="6">
-        <v>62.92</v>
+        <v>65.7878787900817</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
@@ -536,10 +529,10 @@
         <v>45914.0</v>
       </c>
       <c r="B15" s="7">
-        <v>113.0</v>
+        <v>118.0</v>
       </c>
       <c r="C15" s="6">
-        <v>67.76</v>
+        <v>70.8484848508767</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
@@ -547,10 +540,10 @@
         <v>45915.0</v>
       </c>
       <c r="B16" s="7">
-        <v>119.0</v>
+        <v>124.0</v>
       </c>
       <c r="C16" s="6">
-        <v>72.6</v>
+        <v>75.9090909116717</v>
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
@@ -558,10 +551,10 @@
         <v>45916.0</v>
       </c>
       <c r="B17" s="7">
-        <v>123.0</v>
+        <v>131.0</v>
       </c>
       <c r="C17" s="6">
-        <v>77.44</v>
+        <v>80.9696969724667</v>
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
@@ -569,10 +562,10 @@
         <v>45917.0</v>
       </c>
       <c r="B18" s="7">
-        <v>128.0</v>
+        <v>134.0</v>
       </c>
       <c r="C18" s="6">
-        <v>82.28</v>
+        <v>86.0303030332617</v>
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
@@ -580,10 +573,10 @@
         <v>45918.0</v>
       </c>
       <c r="B19" s="7">
-        <v>133.0</v>
+        <v>139.0</v>
       </c>
       <c r="C19" s="6">
-        <v>87.12</v>
+        <v>91.0909090940567</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
@@ -591,10 +584,10 @@
         <v>45919.0</v>
       </c>
       <c r="B20" s="7">
-        <v>142.0</v>
+        <v>144.0</v>
       </c>
       <c r="C20" s="6">
-        <v>91.96</v>
+        <v>96.1515151548517</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
@@ -602,10 +595,10 @@
         <v>45920.0</v>
       </c>
       <c r="B21" s="7">
-        <v>149.0</v>
+        <v>155.0</v>
       </c>
       <c r="C21" s="6">
-        <v>96.8</v>
+        <v>101.212121215647</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
@@ -613,10 +606,10 @@
         <v>45921.0</v>
       </c>
       <c r="B22" s="7">
-        <v>152.0</v>
+        <v>158.0</v>
       </c>
       <c r="C22" s="6">
-        <v>101.64</v>
+        <v>106.272727276442</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
@@ -624,10 +617,10 @@
         <v>45922.0</v>
       </c>
       <c r="B23" s="7">
-        <v>152.0</v>
+        <v>158.0</v>
       </c>
       <c r="C23" s="6">
-        <v>106.48</v>
+        <v>111.333333337237</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
@@ -635,10 +628,10 @@
         <v>45923.0</v>
       </c>
       <c r="B24" s="7">
-        <v>152.0</v>
+        <v>158.0</v>
       </c>
       <c r="C24" s="6">
-        <v>111.32</v>
+        <v>116.393939398032</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
@@ -646,10 +639,10 @@
         <v>45924.0</v>
       </c>
       <c r="B25" s="7">
-        <v>154.0</v>
+        <v>159.0</v>
       </c>
       <c r="C25" s="6">
-        <v>116.16</v>
+        <v>121.454545458827</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
@@ -657,10 +650,10 @@
         <v>45925.0</v>
       </c>
       <c r="B26" s="7">
-        <v>156.0</v>
+        <v>161.0</v>
       </c>
       <c r="C26" s="6">
-        <v>121.0</v>
+        <v>126.515151519622</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
@@ -668,10 +661,10 @@
         <v>45926.0</v>
       </c>
       <c r="B27" s="7">
-        <v>157.0</v>
+        <v>162.0</v>
       </c>
       <c r="C27" s="6">
-        <v>125.84</v>
+        <v>131.575757580417</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
@@ -679,10 +672,10 @@
         <v>45927.0</v>
       </c>
       <c r="B28" s="7">
-        <v>157.0</v>
+        <v>162.0</v>
       </c>
       <c r="C28" s="6">
-        <v>130.68</v>
+        <v>136.636363641212</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
@@ -690,10 +683,10 @@
         <v>45928.0</v>
       </c>
       <c r="B29" s="7">
-        <v>157.0</v>
+        <v>162.0</v>
       </c>
       <c r="C29" s="6">
-        <v>135.52</v>
+        <v>141.696969702007</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
@@ -701,10 +694,10 @@
         <v>45929.0</v>
       </c>
       <c r="B30" s="7">
-        <v>157.0</v>
+        <v>163.0</v>
       </c>
       <c r="C30" s="6">
-        <v>140.36</v>
+        <v>146.757575762802</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
@@ -712,10 +705,10 @@
         <v>45930.0</v>
       </c>
       <c r="B31" s="7">
-        <v>157.0</v>
+        <v>164.0</v>
       </c>
       <c r="C31" s="6">
-        <v>145.2</v>
+        <v>151.818181823597</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
@@ -723,10 +716,10 @@
         <v>45931.0</v>
       </c>
       <c r="B32" s="7">
-        <v>158.0</v>
+        <v>165.0</v>
       </c>
       <c r="C32" s="6">
-        <v>150.04</v>
+        <v>156.878787884392</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
@@ -734,10 +727,10 @@
         <v>45932.0</v>
       </c>
       <c r="B33" s="7">
-        <v>159.0</v>
+        <v>166.0</v>
       </c>
       <c r="C33" s="6">
-        <v>154.88</v>
+        <v>161.939393945187</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
@@ -745,10 +738,10 @@
         <v>45933.0</v>
       </c>
       <c r="B34" s="7">
-        <v>160.0</v>
+        <v>167.0</v>
       </c>
       <c r="C34" s="6">
-        <v>159.72</v>
+        <v>167.000000005982</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1"/>

--- a/INCREMENTO 2/Burn-up.xlsx
+++ b/INCREMENTO 2/Burn-up.xlsx
@@ -34,7 +34,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -44,6 +44,11 @@
     <font>
       <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">
@@ -106,14 +111,16 @@
     <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="5" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" vertical="bottom"/>
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="6" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="7" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="7" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="6" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -389,18 +396,18 @@
         <v>0.0</v>
       </c>
       <c r="C2" s="6">
-        <v>5.06060606061</v>
+        <v>4.84</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="4">
         <v>45902.0</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="7">
         <v>7.0</v>
       </c>
       <c r="C3" s="6">
-        <v>10.1212121212</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
@@ -408,10 +415,10 @@
         <v>45903.0</v>
       </c>
       <c r="B4" s="7">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="C4" s="6">
-        <v>15.1818181822</v>
+        <v>14.52</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
@@ -419,10 +426,10 @@
         <v>45904.0</v>
       </c>
       <c r="B5" s="7">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="C5" s="6">
-        <v>20.2424242429267</v>
+        <v>19.36</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
@@ -430,10 +437,10 @@
         <v>45905.0</v>
       </c>
       <c r="B6" s="7">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="C6" s="6">
-        <v>25.3030303037217</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
@@ -441,10 +448,10 @@
         <v>45906.0</v>
       </c>
       <c r="B7" s="7">
-        <v>36.0</v>
+        <v>35.0</v>
       </c>
       <c r="C7" s="6">
-        <v>30.3636363645167</v>
+        <v>29.04</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
@@ -452,10 +459,10 @@
         <v>45907.0</v>
       </c>
       <c r="B8" s="7">
-        <v>43.0</v>
+        <v>42.0</v>
       </c>
       <c r="C8" s="6">
-        <v>35.4242424253117</v>
+        <v>33.88</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
@@ -463,21 +470,21 @@
         <v>45908.0</v>
       </c>
       <c r="B9" s="7">
-        <v>55.0</v>
+        <v>54.0</v>
       </c>
       <c r="C9" s="6">
-        <v>40.4848484861067</v>
+        <v>38.72</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="4">
         <v>45909.0</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="7">
         <v>66.0</v>
       </c>
       <c r="C10" s="6">
-        <v>45.5454545469017</v>
+        <v>43.56</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
@@ -485,10 +492,10 @@
         <v>45910.0</v>
       </c>
       <c r="B11" s="7">
-        <v>78.0</v>
+        <v>76.0</v>
       </c>
       <c r="C11" s="6">
-        <v>50.6060606076967</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
@@ -496,10 +503,10 @@
         <v>45911.0</v>
       </c>
       <c r="B12" s="7">
-        <v>87.0</v>
+        <v>86.0</v>
       </c>
       <c r="C12" s="6">
-        <v>55.6666666684917</v>
+        <v>53.24</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
@@ -507,21 +514,21 @@
         <v>45912.0</v>
       </c>
       <c r="B13" s="7">
-        <v>98.0</v>
+        <v>94.0</v>
       </c>
       <c r="C13" s="6">
-        <v>60.7272727292867</v>
+        <v>58.08</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="4">
         <v>45913.0</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="7">
         <v>107.0</v>
       </c>
       <c r="C14" s="6">
-        <v>65.7878787900817</v>
+        <v>62.92</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
@@ -529,10 +536,10 @@
         <v>45914.0</v>
       </c>
       <c r="B15" s="7">
-        <v>118.0</v>
+        <v>113.0</v>
       </c>
       <c r="C15" s="6">
-        <v>70.8484848508767</v>
+        <v>67.76</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
@@ -540,10 +547,10 @@
         <v>45915.0</v>
       </c>
       <c r="B16" s="7">
-        <v>124.0</v>
+        <v>119.0</v>
       </c>
       <c r="C16" s="6">
-        <v>75.9090909116717</v>
+        <v>72.6</v>
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
@@ -551,10 +558,10 @@
         <v>45916.0</v>
       </c>
       <c r="B17" s="7">
-        <v>131.0</v>
+        <v>123.0</v>
       </c>
       <c r="C17" s="6">
-        <v>80.9696969724667</v>
+        <v>77.44</v>
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
@@ -562,10 +569,10 @@
         <v>45917.0</v>
       </c>
       <c r="B18" s="7">
-        <v>134.0</v>
+        <v>128.0</v>
       </c>
       <c r="C18" s="6">
-        <v>86.0303030332617</v>
+        <v>82.28</v>
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
@@ -573,10 +580,10 @@
         <v>45918.0</v>
       </c>
       <c r="B19" s="7">
-        <v>139.0</v>
+        <v>133.0</v>
       </c>
       <c r="C19" s="6">
-        <v>91.0909090940567</v>
+        <v>87.12</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
@@ -584,10 +591,10 @@
         <v>45919.0</v>
       </c>
       <c r="B20" s="7">
-        <v>144.0</v>
+        <v>142.0</v>
       </c>
       <c r="C20" s="6">
-        <v>96.1515151548517</v>
+        <v>91.96</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
@@ -595,10 +602,10 @@
         <v>45920.0</v>
       </c>
       <c r="B21" s="7">
-        <v>155.0</v>
+        <v>149.0</v>
       </c>
       <c r="C21" s="6">
-        <v>101.212121215647</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
@@ -606,10 +613,10 @@
         <v>45921.0</v>
       </c>
       <c r="B22" s="7">
-        <v>158.0</v>
+        <v>152.0</v>
       </c>
       <c r="C22" s="6">
-        <v>106.272727276442</v>
+        <v>101.64</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
@@ -617,10 +624,10 @@
         <v>45922.0</v>
       </c>
       <c r="B23" s="7">
-        <v>158.0</v>
+        <v>152.0</v>
       </c>
       <c r="C23" s="6">
-        <v>111.333333337237</v>
+        <v>106.48</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
@@ -628,10 +635,10 @@
         <v>45923.0</v>
       </c>
       <c r="B24" s="7">
-        <v>158.0</v>
+        <v>152.0</v>
       </c>
       <c r="C24" s="6">
-        <v>116.393939398032</v>
+        <v>111.32</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
@@ -639,10 +646,10 @@
         <v>45924.0</v>
       </c>
       <c r="B25" s="7">
-        <v>159.0</v>
+        <v>154.0</v>
       </c>
       <c r="C25" s="6">
-        <v>121.454545458827</v>
+        <v>116.16</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
@@ -650,10 +657,10 @@
         <v>45925.0</v>
       </c>
       <c r="B26" s="7">
-        <v>161.0</v>
+        <v>156.0</v>
       </c>
       <c r="C26" s="6">
-        <v>126.515151519622</v>
+        <v>121.0</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
@@ -661,10 +668,10 @@
         <v>45926.0</v>
       </c>
       <c r="B27" s="7">
-        <v>162.0</v>
+        <v>157.0</v>
       </c>
       <c r="C27" s="6">
-        <v>131.575757580417</v>
+        <v>125.84</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
@@ -672,10 +679,10 @@
         <v>45927.0</v>
       </c>
       <c r="B28" s="7">
-        <v>162.0</v>
+        <v>157.0</v>
       </c>
       <c r="C28" s="6">
-        <v>136.636363641212</v>
+        <v>130.68</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
@@ -683,10 +690,10 @@
         <v>45928.0</v>
       </c>
       <c r="B29" s="7">
-        <v>162.0</v>
+        <v>157.0</v>
       </c>
       <c r="C29" s="6">
-        <v>141.696969702007</v>
+        <v>135.52</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
@@ -694,10 +701,10 @@
         <v>45929.0</v>
       </c>
       <c r="B30" s="7">
-        <v>163.0</v>
+        <v>157.0</v>
       </c>
       <c r="C30" s="6">
-        <v>146.757575762802</v>
+        <v>140.36</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
@@ -705,10 +712,10 @@
         <v>45930.0</v>
       </c>
       <c r="B31" s="7">
-        <v>164.0</v>
+        <v>157.0</v>
       </c>
       <c r="C31" s="6">
-        <v>151.818181823597</v>
+        <v>145.2</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
@@ -716,10 +723,10 @@
         <v>45931.0</v>
       </c>
       <c r="B32" s="7">
-        <v>165.0</v>
+        <v>158.0</v>
       </c>
       <c r="C32" s="6">
-        <v>156.878787884392</v>
+        <v>150.04</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
@@ -727,10 +734,10 @@
         <v>45932.0</v>
       </c>
       <c r="B33" s="7">
-        <v>166.0</v>
+        <v>159.0</v>
       </c>
       <c r="C33" s="6">
-        <v>161.939393945187</v>
+        <v>154.88</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
@@ -738,10 +745,10 @@
         <v>45933.0</v>
       </c>
       <c r="B34" s="7">
-        <v>167.0</v>
+        <v>160.0</v>
       </c>
       <c r="C34" s="6">
-        <v>167.000000005982</v>
+        <v>159.72</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1"/>
